--- a/data/monsters.xlsx
+++ b/data/monsters.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" bestFit="1" customWidth="1" min="4" max="4"/>
@@ -489,6 +489,26 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>drop_item</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>drop_chance</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>drop_min</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>drop_max</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -538,6 +558,20 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>scrap_metal</t>
+        </is>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>첫번째 일반 몬스터(idle 스프라이트 적용)</t>
         </is>
       </c>
@@ -582,6 +616,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>scrap_metal</t>
+        </is>
+      </c>
+      <c r="N3" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>감지 넓고 끈질김</t>
         </is>
       </c>
@@ -625,6 +673,20 @@
         <v>0.9</v>
       </c>
       <c r="M4" t="inlineStr">
+        <is>
+          <t>scrap_metal</t>
+        </is>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q4" t="inlineStr">
         <is>
           <t>빠르지만 약함</t>
         </is>

--- a/data/monsters.xlsx
+++ b/data/monsters.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" bestFit="1" customWidth="1" min="4" max="4"/>
@@ -509,6 +509,16 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
+          <t>is_boss</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>scale</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>note</t>
         </is>
       </c>
@@ -570,7 +580,13 @@
       <c r="P2" t="n">
         <v>2</v>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>첫번째 일반 몬스터(idle 스프라이트 적용)</t>
         </is>
@@ -628,7 +644,13 @@
       <c r="P3" t="n">
         <v>3</v>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="b">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>감지 넓고 끈질김</t>
         </is>
@@ -686,9 +708,84 @@
       <c r="P4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="b">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>빠르지만 약함</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ruins_boss</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>폐허의 파수꾼</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D5" t="n">
+        <v>30</v>
+      </c>
+      <c r="E5" t="n">
+        <v>72</v>
+      </c>
+      <c r="F5" t="n">
+        <v>340</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>90</v>
+      </c>
+      <c r="I5" t="n">
+        <v>28</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>monster_a</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>78</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>scrap_metal</t>
+        </is>
+      </c>
+      <c r="N5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q5" t="b">
+        <v>1</v>
+      </c>
+      <c r="R5" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>지역 보스</t>
         </is>
       </c>
     </row>

--- a/data/monsters.xlsx
+++ b/data/monsters.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:R5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="16" bestFit="1" customWidth="1" min="4" max="4"/>
@@ -494,30 +494,25 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>drop_chance</t>
+          <t>drop_min</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>drop_min</t>
+          <t>drop_max</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>drop_max</t>
+          <t>is_boss</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>is_boss</t>
+          <t>scale</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
-        <is>
-          <t>scale</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -575,18 +570,15 @@
         <v>1</v>
       </c>
       <c r="O2" t="n">
+        <v>2</v>
+      </c>
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q2" t="b">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>첫번째 일반 몬스터(idle 스프라이트 적용)</t>
         </is>
@@ -632,25 +624,22 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>scrap_metal</t>
+          <t>meat</t>
         </is>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
+        <v>3</v>
+      </c>
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q3" t="b">
-        <v>0</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>감지 넓고 끈질김</t>
         </is>
@@ -696,25 +685,22 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>scrap_metal</t>
+          <t>cheese</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="n">
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
         <v>1</v>
       </c>
-      <c r="Q4" t="b">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>빠르지만 약함</t>
         </is>
@@ -769,21 +755,18 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>6</v>
+      </c>
+      <c r="O5" t="n">
+        <v>12</v>
+      </c>
+      <c r="P5" t="b">
         <v>1</v>
       </c>
-      <c r="O5" t="n">
-        <v>6</v>
-      </c>
-      <c r="P5" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q5" t="b">
-        <v>1</v>
-      </c>
-      <c r="R5" t="n">
+      <c r="Q5" t="n">
         <v>2.6</v>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>지역 보스</t>
         </is>
